--- a/business_forms/041_store_audit_checklist_form--business_forms.xlsx
+++ b/business_forms/041_store_audit_checklist_form--business_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,9 +431,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -505,20 +505,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>store_audit_checklist_form_page_1</t>
+          <t>store_conditions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>store_conditions</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Store Conditions</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Evaluate the overall condition of the store.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -528,20 +532,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>store_audit_checklist_form_page_2</t>
+          <t>store_feedback</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>feedback</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Feedback</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please provide feedback on the store's performance.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -551,20 +559,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>store_audit_checklist_form_page_3</t>
+          <t>maintenance_needs</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>maintenance_needs</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Maintenance Needs</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Identify any maintenance needs for the store.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -579,15 +591,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>store_audit_checklist_form_page_4</t>
+          <t>store_security</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>store_security</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Evaluate the store's security status.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -602,15 +618,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>store_audit_checklist_form_page_5</t>
+          <t>store_inventory</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>store_inventory</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Check the store's inventory levels.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -625,15 +645,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>store_audit_checklist_form_page_6</t>
+          <t>store_equipment</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>store_equipment</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Evaluate the store's equipment status.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -648,15 +672,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>store_audit_checklist_form_page_7</t>
+          <t>store_inventory_levels</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>store_inventory_levels</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Inventory Levels</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Check the store's inventory levels status.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -671,15 +699,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>store_audit_checklist_form_page_8</t>
+          <t>store_electrical_systems</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>store_electrical_systems</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Electrical Systems</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Evaluate the store's electrical systems status.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -694,15 +726,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>store_audit_checklist_form_page_9</t>
+          <t>store_waste_disposal</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>store_waste_disposal</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Waste Disposal</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Evaluate the store's waste disposal status.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -717,15 +753,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>store_audit_checklist_form_page_10</t>
+          <t>store_facilities</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>store_facilities</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Evaluate the store's facilities status.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -740,15 +780,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>store_audit_checklist_form_page_11</t>
+          <t>store_electrical_systems_status</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>store_electrical_systems_status</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Electrical Systems Status</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Check the store's electrical systems status.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -763,15 +807,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>store_audit_checklist_form_page_12</t>
+          <t>store_waste_disposal_status</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>store_waste_disposal_status</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Waste Disposal Status</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Check the store's waste disposal status.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -786,15 +834,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>store_audit_checklist_form_page_13</t>
+          <t>store_facilities_status</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>store_facilities_status</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Facilities Status</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Check the store's facilities status.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -809,15 +861,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>store_audit_checklist_form_page_14</t>
+          <t>store_security_status</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>store_security_status</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Security Status</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Check the store's security status.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -832,15 +888,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>store_audit_checklist_form_page_15</t>
+          <t>store_inventory_status</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>store_inventory_status</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Inventory Status</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Check the store's inventory status.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -855,15 +915,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>store_audit_checklist_form_page_16</t>
+          <t>store_equipment_status</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>store_equipment_status</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Equipment Status</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Check the store's equipment status.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -878,15 +942,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>store_audit_checklist_form_page_17</t>
+          <t>store_inventory_levels_status</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>store_inventory_levels_status</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Inventory Levels Status</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Check the store's inventory levels status.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -901,15 +969,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>store_audit_checklist_form_page_18</t>
+          <t>store_electrical_systems_status_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>store_electrical_systems_status</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Store Electrical Systems Status 2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Check the store's electrical systems status.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
@@ -924,15 +996,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>store_audit_checklist_form_page_19</t>
+          <t>store_waste_disposal_status_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>store_waste_disposal_status</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Store Waste Disposal Status 2</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Check the store's waste disposal status.</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>no</t>
@@ -947,15 +1023,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>store_audit_checklist_form_page_20</t>
+          <t>store_facilities_status_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>store_facilities_status</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Store Facilities Status 2</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Check the store's facilities status.</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>no</t>
